--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_navigation.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_navigation.xlsx
@@ -452,36 +452,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Hamburger Menu (Three-line icon that opens a side menu)</t>
+          <t>Full-screen category menu</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>23.5</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Full-screen category menu</t>
+          <t>Hamburger Menu (Three-line icon that opens a side menu)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>5.5</v>
+        <v>4.91</v>
       </c>
     </row>
   </sheetData>
